--- a/output/topology_excel/11206.xlsx
+++ b/output/topology_excel/11206.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,10 +572,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B9" t="n">
         <v>11</v>
@@ -638,10 +638,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B11" t="n">
         <v>12</v>
@@ -682,156 +682,156 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>434</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>123</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>191</v>
+        <v>370</v>
       </c>
       <c r="F17" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -839,329 +839,21 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wall</t>
+          <t>Opening</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>209</v>
+        <v>111</v>
       </c>
       <c r="F19" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" t="n">
-        <v>10</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>309</v>
-      </c>
-      <c r="F20" t="n">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" t="n">
-        <v>11</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>125</v>
-      </c>
-      <c r="F21" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" t="n">
-        <v>12</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
-        <v>107</v>
-      </c>
-      <c r="F22" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" t="n">
-        <v>4</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>162</v>
-      </c>
-      <c r="F23" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>4</v>
-      </c>
-      <c r="B24" t="n">
-        <v>5</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>162</v>
-      </c>
-      <c r="F24" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>5</v>
-      </c>
-      <c r="B25" t="n">
-        <v>11</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>235</v>
-      </c>
-      <c r="F25" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>6</v>
-      </c>
-      <c r="B26" t="n">
-        <v>7</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
-        <v>146</v>
-      </c>
-      <c r="F26" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>6</v>
-      </c>
-      <c r="B27" t="n">
-        <v>9</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
-        <v>328</v>
-      </c>
-      <c r="F27" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>7</v>
-      </c>
-      <c r="B28" t="n">
-        <v>8</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
-        <v>146</v>
-      </c>
-      <c r="F28" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>7</v>
-      </c>
-      <c r="B29" t="n">
-        <v>9</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
-        <v>123</v>
-      </c>
-      <c r="F29" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>8</v>
-      </c>
-      <c r="B30" t="n">
-        <v>9</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>122</v>
-      </c>
-      <c r="F30" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>9</v>
-      </c>
-      <c r="B31" t="n">
-        <v>12</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="n">
-        <v>104</v>
-      </c>
-      <c r="F31" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>10</v>
-      </c>
-      <c r="B32" t="n">
-        <v>11</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" t="n">
-        <v>302</v>
-      </c>
-      <c r="F32" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>10</v>
-      </c>
-      <c r="B33" t="n">
-        <v>12</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="n">
-        <v>104</v>
-      </c>
-      <c r="F33" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/11206.xlsx
+++ b/output/topology_excel/11206.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>14</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>14</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>13</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>11</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>14</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>14</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>17</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>15</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>30</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>15</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -693,22 +723,28 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B13" t="n">
         <v>3</v>
       </c>
-      <c r="B13" t="n">
-        <v>10</v>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>Opening</t>
@@ -718,18 +754,20 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>231</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,18 +778,20 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>231</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>1</v>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -762,18 +802,20 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,15 +826,17 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>183</v>
+        <v>370</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B17" t="n">
         <v>11</v>
@@ -806,15 +850,17 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>370</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B18" t="n">
         <v>11</v>
@@ -828,33 +874,13 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" t="n">
-        <v>11</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
-        <v>111</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
